--- a/vehicle.xlsx
+++ b/vehicle.xlsx
@@ -11,147 +11,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1" uniqueCount="1">
   <si>
     <t>vehicleNumber</t>
-  </si>
-  <si>
-    <t>MP09AL4117</t>
-  </si>
-  <si>
-    <t>MP09AL4126</t>
-  </si>
-  <si>
-    <t>MP09AL4130</t>
-  </si>
-  <si>
-    <t>MP09AL4132</t>
-  </si>
-  <si>
-    <t>MP09AL4160</t>
-  </si>
-  <si>
-    <t>MP09AR0428</t>
-  </si>
-  <si>
-    <t>MP09AR0443</t>
-  </si>
-  <si>
-    <t>MP09AR0473</t>
-  </si>
-  <si>
-    <t>MP09BK1620</t>
-  </si>
-  <si>
-    <t>MP09BK1677</t>
-  </si>
-  <si>
-    <t>MP09BK2588</t>
-  </si>
-  <si>
-    <t>MP09DC1106</t>
-  </si>
-  <si>
-    <t>MP09DC1108</t>
-  </si>
-  <si>
-    <t>MP09DC1127</t>
-  </si>
-  <si>
-    <t>MP09DC1135</t>
-  </si>
-  <si>
-    <t>MP09DG4991</t>
-  </si>
-  <si>
-    <t>MP09DJ5053</t>
-  </si>
-  <si>
-    <t>MP09DJ5081</t>
-  </si>
-  <si>
-    <t>MP09DJ9062</t>
-  </si>
-  <si>
-    <t>MP09DT3096</t>
-  </si>
-  <si>
-    <t>MP09DT3921</t>
-  </si>
-  <si>
-    <t>MP09DT3930</t>
-  </si>
-  <si>
-    <t>MP09DT3975</t>
-  </si>
-  <si>
-    <t>MP09DT3986</t>
-  </si>
-  <si>
-    <t>MP09GH1505</t>
-  </si>
-  <si>
-    <t>MP09GH1506</t>
-  </si>
-  <si>
-    <t>MP09GH9622</t>
-  </si>
-  <si>
-    <t>MP09GJ0125</t>
-  </si>
-  <si>
-    <t>MP09GJ0933</t>
-  </si>
-  <si>
-    <t>MP09HH6047</t>
-  </si>
-  <si>
-    <t>MP09HH9717</t>
-  </si>
-  <si>
-    <t>MP09HJ0137</t>
-  </si>
-  <si>
-    <t>MP09HJ0138</t>
-  </si>
-  <si>
-    <t>MP09ZN4415</t>
-  </si>
-  <si>
-    <t>MP09ZN4498</t>
-  </si>
-  <si>
-    <t>MP09ZQ0712</t>
-  </si>
-  <si>
-    <t>MP09ZQ0725</t>
-  </si>
-  <si>
-    <t>MP09ZQ4541</t>
-  </si>
-  <si>
-    <t>MP09ZQ4551</t>
-  </si>
-  <si>
-    <t>MP09ZY4210</t>
-  </si>
-  <si>
-    <t>MP09ZY4232</t>
-  </si>
-  <si>
-    <t>MP09ZY4281</t>
-  </si>
-  <si>
-    <t>MP09ZY4289</t>
-  </si>
-  <si>
-    <t>MP09ZZ6191</t>
-  </si>
-  <si>
-    <t>MP09ZZ6242</t>
-  </si>
-  <si>
-    <t>MP09ZZ6254</t>
   </si>
 </sst>
 </file>
@@ -528,7 +390,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:A47"/>
+  <dimension ref="A1:A1"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="30" customWidth="1"/>
@@ -539,236 +401,6 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A23" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A24" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A25" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A26" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A27" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A28" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="29" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A29" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="30" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A30" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="31" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A31" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="32" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A32" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A33" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="34" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A34" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="35" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A35" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="36" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A36" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="37" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A37" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="38" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A38" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="39" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A39" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="40" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A40" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="41" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A41" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="42" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A42" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="43" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A43" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="44" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A44" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="45" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A45" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="46" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A46" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="47" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A47" t="s">
-        <v>46</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
